--- a/media/Levels/kakeraMapLevel2.xlsx
+++ b/media/Levels/kakeraMapLevel2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD18473-B5F6-43E2-91E4-7BCEB2060967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8C44D8-1873-499B-BBFD-0B57E4039676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
+    <workbookView xWindow="2532" yWindow="84" windowWidth="15660" windowHeight="12168" xr2:uid="{351F5D84-BB1C-441C-AD4F-89307D46543D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19147,28 +19147,28 @@
         <v>0</v>
       </c>
       <c r="AU62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC62">
         <v>0</v>
@@ -19452,28 +19452,28 @@
         <v>0</v>
       </c>
       <c r="AU63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC63">
         <v>0</v>
@@ -19757,28 +19757,28 @@
         <v>0</v>
       </c>
       <c r="AU64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC64">
         <v>0</v>
@@ -20062,28 +20062,28 @@
         <v>0</v>
       </c>
       <c r="AU65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC65">
         <v>0</v>
@@ -20367,28 +20367,28 @@
         <v>0</v>
       </c>
       <c r="AU66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC66">
         <v>0</v>
@@ -20672,28 +20672,28 @@
         <v>0</v>
       </c>
       <c r="AU67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC67">
         <v>0</v>
@@ -20977,28 +20977,28 @@
         <v>0</v>
       </c>
       <c r="AU68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC68">
         <v>0</v>
@@ -21282,28 +21282,28 @@
         <v>0</v>
       </c>
       <c r="AU69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC69">
         <v>0</v>
@@ -21587,28 +21587,28 @@
         <v>0</v>
       </c>
       <c r="AU70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC70">
         <v>0</v>
